--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484711_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484711_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0862</v>
+        <v>3.8341</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5513</v>
+        <v>2.9024</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5349</v>
+        <v>0.9317</v>
       </c>
       <c r="G2" t="n">
         <v>3.4394</v>
@@ -610,13 +610,13 @@
         <v>1.887</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0512</v>
+        <v>0.6967</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2787</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2275</v>
+        <v>0.6243</v>
       </c>
       <c r="V2" t="n">
         <v>1.585</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.393</v>
+        <v>1.9924</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3276</v>
+        <v>2.1916</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0653</v>
+        <v>-0.1992</v>
       </c>
       <c r="G3" t="n">
         <v>0.4856</v>
@@ -688,13 +688,13 @@
         <v>1.3209</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4849</v>
+        <v>1.0843</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7236</v>
+        <v>0.5875</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7613</v>
+        <v>0.4968</v>
       </c>
       <c r="V3" t="n">
         <v>0.9886</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.0548</v>
       </c>
       <c r="E5" t="n">
-        <v>1.852</v>
+        <v>1.2674</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9746</v>
+        <v>-1.2127</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3534</v>
@@ -844,13 +844,13 @@
         <v>1.1322</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2797</v>
+        <v>0.4571</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0175</v>
+        <v>0.4329</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2622</v>
+        <v>0.0241</v>
       </c>
       <c r="V5" t="n">
         <v>-1.181</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3626</v>
+        <v>-1.1955</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6403</v>
+        <v>-0.7377</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7223000000000001</v>
+        <v>-0.4578</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4165</v>
@@ -922,13 +922,13 @@
         <v>1.887</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0218</v>
+        <v>0.1453</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1328</v>
+        <v>0.0354</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1546</v>
+        <v>0.11</v>
       </c>
       <c r="V6" t="n">
         <v>-1.8678</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>U. ZAMORA MANA</t>
+          <t>S. JIMENA LLORCA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8126</v>
+        <v>-1.7027</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4223</v>
+        <v>-0.9645</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3903</v>
+        <v>-0.7382</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9782</v>
+        <v>0.8078</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0322</v>
+        <v>-0.2982</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.946</v>
+        <v>1.106</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1638</v>
+        <v>1.8664</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1526</v>
+        <v>1.2154</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.0112</v>
+        <v>0.651</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8144</v>
+        <v>-1.0586</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8796</v>
+        <v>-1.5135</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.455</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3774</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.887</v>
+        <v>-2.8305</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5096</v>
+        <v>1.6983</v>
       </c>
       <c r="S7" t="n">
-        <v>1.7882</v>
+        <v>0.4253</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3267</v>
+        <v>-0.0004</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4615</v>
+        <v>0.4257</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2452</v>
+        <v>-1.8036</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.547</v>
+        <v>-1.8036</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. JIMENA LLORCA</t>
+          <t>U. ZAMORA MANA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2209</v>
+        <v>-2.2591</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2181</v>
+        <v>-1.9482</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0028</v>
+        <v>-0.3109</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8078</v>
+        <v>-1.9782</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2982</v>
+        <v>-1.0322</v>
       </c>
       <c r="I8" t="n">
-        <v>1.106</v>
+        <v>-0.946</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8664</v>
+        <v>-1.1638</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2154</v>
+        <v>-0.1526</v>
       </c>
       <c r="L8" t="n">
-        <v>0.651</v>
+        <v>-1.0112</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0586</v>
+        <v>-0.8144</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5135</v>
+        <v>-0.8796</v>
       </c>
       <c r="O8" t="n">
-        <v>0.455</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1322</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.8305</v>
+        <v>-1.887</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6983</v>
+        <v>1.5096</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0929</v>
+        <v>1.3418</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.254</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1611</v>
+        <v>0.5409</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8036</v>
+        <v>-1.2452</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.8036</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0532</v>
+        <v>-2.4278</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0039</v>
+        <v>-0.4579</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0493</v>
+        <v>-1.9699</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9249</v>
@@ -1156,13 +1156,13 @@
         <v>0.5661</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5132</v>
+        <v>0.1121</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5632</v>
+        <v>-0.0172</v>
       </c>
       <c r="U9" t="n">
-        <v>0.05</v>
+        <v>0.1294</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2377</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0912</v>
+        <v>-2.9215</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2615</v>
+        <v>-1.7743</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8297</v>
+        <v>-1.1472</v>
       </c>
       <c r="G10" t="n">
         <v>1.296</v>
@@ -1234,13 +1234,13 @@
         <v>0.3774</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2093</v>
+        <v>0.379</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6808</v>
+        <v>-0.1936</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8901</v>
+        <v>0.5726</v>
       </c>
       <c r="V10" t="n">
         <v>-2.1434</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7657</v>
+        <v>-4.0302</v>
       </c>
       <c r="E11" t="n">
         <v>-3.585</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1807</v>
+        <v>-0.4452</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6235</v>
@@ -1312,13 +1312,13 @@
         <v>0.9435</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9899</v>
+        <v>0.7254</v>
       </c>
       <c r="T11" t="n">
         <v>0.0276</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9624</v>
+        <v>0.6978</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2452</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.015600000000003</v>
+        <v>-7.7216</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.466299999999999</v>
+        <v>-2.1723</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.549499999999999</v>
+        <v>-5.549399999999999</v>
       </c>
       <c r="G12" t="n">
         <v>0.6661999999999999</v>
@@ -1390,13 +1390,13 @@
         <v>11.322</v>
       </c>
       <c r="S12" t="n">
-        <v>5.072900000000001</v>
+        <v>5.367000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4515</v>
+        <v>1.7455</v>
       </c>
       <c r="U12" t="n">
-        <v>3.6215</v>
+        <v>3.6216</v>
       </c>
       <c r="V12" t="n">
         <v>-7.150300000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. GOODMAN</t>
+          <t>D. SARRIAS SANCHEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.8185</v>
+        <v>5.0145</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9339</v>
+        <v>4.4364</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1154</v>
+        <v>0.5782</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5176</v>
+        <v>3.1301</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6451</v>
+        <v>2.0653</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.1275</v>
+        <v>1.0649</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8085</v>
+        <v>4.7073</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7674</v>
+        <v>2.8635</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0411</v>
+        <v>1.8438</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.2909</v>
+        <v>-1.5772</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1222</v>
+        <v>-0.7982</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1687</v>
+        <v>-0.7789</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1887</v>
+        <v>0.7548</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2644</v>
+        <v>-1.1322</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0757</v>
+        <v>1.887</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8306</v>
+        <v>-0.7572</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2323</v>
+        <v>-0.3839</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5984</v>
+        <v>-0.3732</v>
       </c>
       <c r="V13" t="n">
-        <v>4.3202</v>
+        <v>1.8868</v>
       </c>
       <c r="W13" t="n">
-        <v>4.6221</v>
+        <v>1.2452</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3018</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. SARRIAS SANCHEZ</t>
+          <t>T. GOODMAN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6706</v>
+        <v>4.9508</v>
       </c>
       <c r="E14" t="n">
-        <v>4.8261</v>
+        <v>5.9339</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1554</v>
+        <v>-0.9831</v>
       </c>
       <c r="G14" t="n">
-        <v>3.1301</v>
+        <v>1.5176</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0653</v>
+        <v>2.6451</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0649</v>
+        <v>-1.1275</v>
       </c>
       <c r="J14" t="n">
-        <v>4.7073</v>
+        <v>3.8085</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8635</v>
+        <v>3.7674</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8438</v>
+        <v>0.0411</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5772</v>
+        <v>-2.2909</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7982</v>
+        <v>-1.1222</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7789</v>
+        <v>-1.1687</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7548</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1322</v>
+        <v>-2.2644</v>
       </c>
       <c r="R14" t="n">
-        <v>1.887</v>
+        <v>2.0757</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1011</v>
+        <v>-0.6984</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0058</v>
+        <v>-0.2323</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1069</v>
+        <v>-0.4661</v>
       </c>
       <c r="V14" t="n">
-        <v>1.8868</v>
+        <v>4.3202</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2452</v>
+        <v>4.6221</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6415999999999999</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. CARR</t>
+          <t>A. FERRAGUT SEBASTIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8331</v>
+        <v>4.2434</v>
       </c>
       <c r="E15" t="n">
-        <v>4.332</v>
+        <v>3.901</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4989</v>
+        <v>0.3424</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4161</v>
+        <v>1.3962</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9743000000000001</v>
+        <v>1.0862</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5583</v>
+        <v>0.31</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4158</v>
+        <v>3.3146</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3251</v>
+        <v>2.6154</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.6992</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9998</v>
+        <v>-1.9184</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3507</v>
+        <v>-1.5292</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.649</v>
+        <v>-0.3892</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5096</v>
+        <v>2.8305</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.887</v>
+        <v>-0.3774</v>
       </c>
       <c r="R15" t="n">
-        <v>3.3966</v>
+        <v>3.2079</v>
       </c>
       <c r="S15" t="n">
-        <v>0.964</v>
+        <v>-0.587</v>
       </c>
       <c r="T15" t="n">
-        <v>1.011</v>
+        <v>-0.8851</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0469</v>
+        <v>0.2981</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9434</v>
+        <v>0.6036</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7922</v>
+        <v>1.8488</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8488</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. FERRAGUT SEBASTIA</t>
+          <t>J. CARR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.69</v>
+        <v>2.9502</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3163</v>
+        <v>3.1628</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3736</v>
+        <v>-0.2127</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3962</v>
+        <v>0.4161</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0862</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.31</v>
+        <v>-0.5583</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3146</v>
+        <v>2.4158</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6154</v>
+        <v>2.3251</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6992</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.9184</v>
+        <v>-1.9998</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5292</v>
+        <v>-1.3507</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3892</v>
+        <v>-0.649</v>
       </c>
       <c r="P16" t="n">
-        <v>2.8305</v>
+        <v>1.5096</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.3774</v>
+        <v>-1.887</v>
       </c>
       <c r="R16" t="n">
-        <v>3.2079</v>
+        <v>3.3966</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1404</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4697</v>
+        <v>-0.1582</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3293</v>
+        <v>0.2393</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6036</v>
+        <v>0.9434</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8488</v>
+        <v>2.7922</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2452</v>
+        <v>-1.8488</v>
       </c>
     </row>
     <row r="17">
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. RHAIEM SANCHEZ</t>
+          <t>S. SUAREZ BELLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5219</v>
+        <v>0.5374</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4543</v>
+        <v>0.2832</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0675</v>
+        <v>0.2542</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0193</v>
+        <v>0.6851</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7615</v>
+        <v>0.5768</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2578</v>
+        <v>0.1083</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5836</v>
+        <v>0.7396</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5425</v>
+        <v>0.7396</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0411</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5643</v>
+        <v>-0.0544</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.781</v>
+        <v>-0.1628</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2167</v>
+        <v>0.1083</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3774</v>
+        <v>0.1887</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1322</v>
+        <v>-0.3774</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5096</v>
+        <v>0.5661</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3704</v>
+        <v>-0.3364</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0029</v>
+        <v>-0.0789</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3675</v>
+        <v>-0.2575</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. SUAREZ BELLO</t>
+          <t>E. RHAIEM SANCHEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3606</v>
+        <v>0.2188</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1858</v>
+        <v>0.2595</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1748</v>
+        <v>-0.0406</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6851</v>
+        <v>1.0193</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5768</v>
+        <v>0.7615</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1083</v>
+        <v>0.2578</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7396</v>
+        <v>1.5836</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7396</v>
+        <v>1.5425</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0411</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0544</v>
+        <v>-0.5643</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1628</v>
+        <v>-0.781</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1083</v>
+        <v>0.2167</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1887</v>
+        <v>0.3774</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.3774</v>
+        <v>-1.1322</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5661</v>
+        <v>1.5096</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5132</v>
+        <v>0.0673</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1764</v>
+        <v>-0.192</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3368</v>
+        <v>0.2593</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8101</v>
+        <v>-0.6008</v>
       </c>
       <c r="E20" t="n">
         <v>-1.0188</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2087</v>
+        <v>0.418</v>
       </c>
       <c r="G20" t="n">
         <v>0.1393</v>
@@ -2014,13 +2014,13 @@
         <v>0.1887</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1946</v>
+        <v>0.0147</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1176</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.077</v>
+        <v>0.1323</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5485</v>
+        <v>-3.6271</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.8725</v>
+        <v>-5.2879</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3239</v>
+        <v>1.6608</v>
       </c>
       <c r="G21" t="n">
         <v>-4.554</v>
@@ -2092,13 +2092,13 @@
         <v>2.8305</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7118</v>
+        <v>-0.7904</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3521</v>
+        <v>-0.7675</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3597</v>
+        <v>-0.0229</v>
       </c>
       <c r="V21" t="n">
         <v>0.019</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.4713</v>
+        <v>-4.6737</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.5586</v>
+        <v>-7.0714</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0873</v>
+        <v>2.3977</v>
       </c>
       <c r="G22" t="n">
         <v>-5.3668</v>
@@ -2170,13 +2170,13 @@
         <v>2.2644</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-0.1183</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2933</v>
+        <v>-0.8062</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3775</v>
+        <v>0.6879</v>
       </c>
       <c r="V22" t="n">
         <v>0.6226</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>8.015699999999999</v>
+        <v>9.964399999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>5.5494</v>
+        <v>5.549600000000003</v>
       </c>
       <c r="F23" t="n">
-        <v>2.4661</v>
+        <v>4.414899999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6661999999999999</v>
@@ -2248,13 +2248,13 @@
         <v>17.9265</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.0731</v>
+        <v>-3.1246</v>
       </c>
       <c r="T23" t="n">
         <v>-3.6217</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.4514</v>
+        <v>0.4972</v>
       </c>
       <c r="V23" t="n">
         <v>7.150399999999999</v>
